--- a/data/trans_orig/P1804_2016_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1804_2016_2023-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20516</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43409</t>
+          <t>43321</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34272</t>
+          <t>33243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60492</t>
+          <t>60556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58822</t>
+          <t>61517</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95933</t>
+          <t>96558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>385683</t>
+          <t>385771</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>408576</t>
+          <t>408183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286563</t>
+          <t>286499</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312783</t>
+          <t>313812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>680214</t>
+          <t>679589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>717325</t>
+          <t>714630</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>10506</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28080</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27967</t>
+          <t>27032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55102</t>
+          <t>52316</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>42434</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72612</t>
+          <t>73948</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>349147</t>
+          <t>349157</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366586</t>
+          <t>366721</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317171</t>
+          <t>319957</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>344306</t>
+          <t>345241</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>676888</t>
+          <t>675552</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>707013</t>
+          <t>707066</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22622</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45375</t>
+          <t>45137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11980</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29664</t>
+          <t>29116</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39262</t>
+          <t>40259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68158</t>
+          <t>69566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>476539</t>
+          <t>476777</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>499292</t>
+          <t>499179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136459</t>
+          <t>137007</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154143</t>
+          <t>153606</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>619878</t>
+          <t>618470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>648774</t>
+          <t>647777</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63714</t>
+          <t>63789</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97630</t>
+          <t>98250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67454</t>
+          <t>67347</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103752</t>
+          <t>102997</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141489</t>
+          <t>139849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195265</t>
+          <t>189301</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1052008</t>
+          <t>1051388</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1085924</t>
+          <t>1085849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>722124</t>
+          <t>722879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>758422</t>
+          <t>758529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1780249</t>
+          <t>1786213</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1834025</t>
+          <t>1835665</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>25196</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49203</t>
+          <t>48209</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57925</t>
+          <t>56708</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88306</t>
+          <t>89622</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88121</t>
+          <t>89371</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130250</t>
+          <t>131164</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>571503</t>
+          <t>572497</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>596074</t>
+          <t>595510</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>649938</t>
+          <t>648622</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>680319</t>
+          <t>681536</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1228700</t>
+          <t>1227786</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1270829</t>
+          <t>1269579</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>25170</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72895</t>
+          <t>71863</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113898</t>
+          <t>113426</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86905</t>
+          <t>87366</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130388</t>
+          <t>132828</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261300</t>
+          <t>261975</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>278019</t>
+          <t>277240</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>968127</t>
+          <t>968599</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1009130</t>
+          <t>1010162</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1238782</t>
+          <t>1236342</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1282265</t>
+          <t>1281804</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>188124</t>
+          <t>187712</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>243011</t>
+          <t>242939</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>317385</t>
+          <t>313927</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>389446</t>
+          <t>389572</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>521789</t>
+          <t>521037</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>615347</t>
+          <t>616061</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3142711</t>
+          <t>3142783</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3197598</t>
+          <t>3198010</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3142150</t>
+          <t>3142024</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3214211</t>
+          <t>3217669</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6301971</t>
+          <t>6301257</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6395529</t>
+          <t>6396281</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -3361,32 +3361,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>41327</t>
+          <t>48713</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31106</t>
+          <t>34914</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54548</t>
+          <t>65035</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3396,32 +3396,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49074</t>
+          <t>54535</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39395</t>
+          <t>43197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62736</t>
+          <t>68538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3431,32 +3431,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>90402</t>
+          <t>103248</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75277</t>
+          <t>84890</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109286</t>
+          <t>123282</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -3474,32 +3474,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>463885</t>
+          <t>501905</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>450664</t>
+          <t>485583</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>474106</t>
+          <t>515704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3509,32 +3509,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>398230</t>
+          <t>431474</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>384568</t>
+          <t>417471</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>407909</t>
+          <t>442812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3544,32 +3544,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>862114</t>
+          <t>933379</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>843230</t>
+          <t>913345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>877239</t>
+          <t>951737</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,81%</t>
         </is>
       </c>
     </row>
@@ -3587,17 +3587,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3622,17 +3622,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447304</t>
+          <t>486009</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447304</t>
+          <t>486009</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447304</t>
+          <t>486009</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952516</t>
+          <t>1036627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952516</t>
+          <t>1036627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952516</t>
+          <t>1036627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3704,22 +3704,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40996</t>
+          <t>45011</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29022</t>
+          <t>31036</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56964</t>
+          <t>63568</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3739,22 +3739,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42048</t>
+          <t>47437</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32786</t>
+          <t>36247</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55156</t>
+          <t>61300</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3774,32 +3774,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>83044</t>
+          <t>92447</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66868</t>
+          <t>74918</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102937</t>
+          <t>113278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -3817,27 +3817,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>411217</t>
+          <t>438201</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>395249</t>
+          <t>419644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423191</t>
+          <t>452176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3852,27 +3852,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>340532</t>
+          <t>375706</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327424</t>
+          <t>361843</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>349794</t>
+          <t>386896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3887,32 +3887,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>751749</t>
+          <t>813908</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731856</t>
+          <t>793077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>767925</t>
+          <t>831437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -3930,17 +3930,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4000,17 +4000,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4047,32 +4047,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30255</t>
+          <t>36552</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>24944</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53899</t>
+          <t>51603</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4082,32 +4082,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14977</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24185</t>
+          <t>28410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4117,32 +4117,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>45232</t>
+          <t>54022</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20427</t>
+          <t>40263</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70821</t>
+          <t>71492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -4160,32 +4160,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>638009</t>
+          <t>435060</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614365</t>
+          <t>420009</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657732</t>
+          <t>446668</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4195,32 +4195,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>151934</t>
+          <t>170027</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142726</t>
+          <t>159087</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157385</t>
+          <t>176540</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4230,32 +4230,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>789943</t>
+          <t>605087</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>764354</t>
+          <t>587617</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>814748</t>
+          <t>618846</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -4273,17 +4273,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4308,17 +4308,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4343,17 +4343,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4390,32 +4390,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42112</t>
+          <t>49264</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30767</t>
+          <t>36733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55981</t>
+          <t>67785</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4425,32 +4425,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62909</t>
+          <t>75307</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30065</t>
+          <t>59828</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87228</t>
+          <t>90575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4460,32 +4460,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>105021</t>
+          <t>124570</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76030</t>
+          <t>103368</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131142</t>
+          <t>147883</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -4503,32 +4503,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>992707</t>
+          <t>1082579</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>978838</t>
+          <t>1064058</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1004052</t>
+          <t>1095110</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4538,32 +4538,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>914457</t>
+          <t>784392</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>890138</t>
+          <t>769124</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>947301</t>
+          <t>799871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4573,32 +4573,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1907164</t>
+          <t>1866972</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1881043</t>
+          <t>1843659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1936155</t>
+          <t>1888174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977366</t>
+          <t>859699</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977366</t>
+          <t>859699</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977366</t>
+          <t>859699</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012185</t>
+          <t>1991542</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012185</t>
+          <t>1991542</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012185</t>
+          <t>1991542</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4733,32 +4733,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>30544</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17395</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43651</t>
+          <t>47726</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4768,32 +4768,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>61651</t>
+          <t>69639</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44568</t>
+          <t>55991</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77458</t>
+          <t>85606</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4803,32 +4803,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>90362</t>
+          <t>100183</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69676</t>
+          <t>83479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109851</t>
+          <t>121592</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -4846,32 +4846,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>446335</t>
+          <t>537420</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>431395</t>
+          <t>520238</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>457651</t>
+          <t>548939</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4881,32 +4881,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>779684</t>
+          <t>761211</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>763877</t>
+          <t>745244</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>796767</t>
+          <t>774859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4916,32 +4916,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1226019</t>
+          <t>1298631</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1206530</t>
+          <t>1277222</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1246705</t>
+          <t>1315335</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -4959,17 +4959,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5029,17 +5029,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5076,32 +5076,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5111,27 +5111,27 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>36397</t>
+          <t>41182</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28191</t>
+          <t>31750</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47331</t>
+          <t>52528</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5146,32 +5146,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>40077</t>
+          <t>44961</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30600</t>
+          <t>35484</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51280</t>
+          <t>59646</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -5189,32 +5189,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>236827</t>
+          <t>233450</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227499</t>
+          <t>225686</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239923</t>
+          <t>236500</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5224,22 +5224,22 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>722068</t>
+          <t>800190</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>711134</t>
+          <t>788844</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>730274</t>
+          <t>809622</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5259,32 +5259,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>958895</t>
+          <t>1033639</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>947692</t>
+          <t>1018954</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>968372</t>
+          <t>1043116</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -5302,17 +5302,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>758465</t>
+          <t>841372</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>758465</t>
+          <t>841372</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>758465</t>
+          <t>841372</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5372,17 +5372,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>998972</t>
+          <t>1078600</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>998972</t>
+          <t>1078600</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>998972</t>
+          <t>1078600</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>187080</t>
+          <t>213862</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>143217</t>
+          <t>183858</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>222081</t>
+          <t>249448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5454,32 +5454,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>267056</t>
+          <t>305569</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>218016</t>
+          <t>277064</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>301840</t>
+          <t>338050</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5489,32 +5489,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>454136</t>
+          <t>519431</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>393758</t>
+          <t>473049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>507416</t>
+          <t>566256</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -5532,32 +5532,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3188980</t>
+          <t>3228614</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3153979</t>
+          <t>3193028</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3232843</t>
+          <t>3258618</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5567,32 +5567,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3306905</t>
+          <t>3323000</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3272121</t>
+          <t>3290519</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3355945</t>
+          <t>3351505</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5602,32 +5602,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6495886</t>
+          <t>6551614</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6442606</t>
+          <t>6504789</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6556264</t>
+          <t>6597996</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -5645,17 +5645,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5680,17 +5680,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573961</t>
+          <t>3628569</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573961</t>
+          <t>3628569</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573961</t>
+          <t>3628569</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5715,17 +5715,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6950022</t>
+          <t>7071045</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6950022</t>
+          <t>7071045</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6950022</t>
+          <t>7071045</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
